--- a/thaco/color/Office-1_color_ DATA.xlsx
+++ b/thaco/color/Office-1_color_ DATA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adity/Documents/GitHub/gitlocal/thaco/color/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{510AEE7C-AAA1-594C-ACC7-73573FB3963C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8AF05A3-851C-ED44-9D8E-303DCF1A0F47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="42900" yWindow="2680" windowWidth="33760" windowHeight="18480" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bảng lương CB-NV" sheetId="5" r:id="rId1"/>
@@ -4533,9 +4533,6 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>Net Pay Period 1</t>
-  </si>
-  <si>
     <t>Accounting department</t>
   </si>
   <si>
@@ -4549,6 +4546,9 @@
   </si>
   <si>
     <t>Digital Transformation Department</t>
+  </si>
+  <si>
+    <t>Realization part 1</t>
   </si>
 </sst>
 </file>
@@ -5521,7 +5521,7 @@
         <v>32</v>
       </c>
       <c r="AP1" s="64" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="AQ1" s="65" t="s">
         <v>14</v>
@@ -5550,7 +5550,7 @@
         <v>55</v>
       </c>
       <c r="C2" s="35" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D2" s="36" t="s">
         <v>47</v>
@@ -5656,7 +5656,7 @@
         <v>56</v>
       </c>
       <c r="C3" s="35" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D3" s="36" t="s">
         <v>47</v>
@@ -5762,7 +5762,7 @@
         <v>57</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D4" s="36" t="s">
         <v>47</v>
@@ -5868,7 +5868,7 @@
         <v>58</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D5" s="36" t="s">
         <v>47</v>
@@ -5976,7 +5976,7 @@
         <v>59</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D6" s="36" t="s">
         <v>47</v>
@@ -6084,7 +6084,7 @@
         <v>60</v>
       </c>
       <c r="C7" s="35" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D7" s="36" t="s">
         <v>52</v>
@@ -6194,7 +6194,7 @@
         <v>62</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D8" s="36" t="s">
         <v>47</v>
